--- a/backend/data/financials_by_company/1252.HK.xlsx
+++ b/backend/data/financials_by_company/1252.HK.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-151540000</v>
+        <v>1557580.550725</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.118079</v>
       </c>
       <c r="D2" t="n">
-        <v>2789821000</v>
+        <v>3629965000</v>
       </c>
       <c r="E2" t="n">
-        <v>-531817000</v>
+        <v>13191000</v>
       </c>
       <c r="F2" t="n">
-        <v>-606160000</v>
+        <v>13191000</v>
       </c>
       <c r="G2" t="n">
-        <v>279412000</v>
+        <v>1200590000</v>
       </c>
       <c r="H2" t="n">
-        <v>856431000</v>
+        <v>1188599000</v>
       </c>
       <c r="I2" t="n">
-        <v>4770426000</v>
+        <v>9482950000</v>
       </c>
       <c r="J2" t="n">
-        <v>2258004000</v>
+        <v>3643156000</v>
       </c>
       <c r="K2" t="n">
-        <v>1401573000</v>
+        <v>2454557000</v>
       </c>
       <c r="L2" t="n">
-        <v>498025000</v>
+        <v>-908708000</v>
       </c>
       <c r="M2" t="n">
-        <v>922872000</v>
+        <v>1001454000</v>
       </c>
       <c r="N2" t="n">
-        <v>1420897000</v>
+        <v>92746000</v>
       </c>
       <c r="O2" t="n">
-        <v>808375000</v>
+        <v>1188956580.550725</v>
       </c>
       <c r="P2" t="n">
-        <v>279412000</v>
+        <v>1200590000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5516523000</v>
+        <v>10504042000</v>
       </c>
       <c r="R2" t="n">
         <v>2938282000</v>
@@ -719,142 +719,144 @@
         <v>2938282000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>0.41</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.41</v>
+      </c>
       <c r="V2" t="n">
-        <v>279412000</v>
+        <v>1200590000</v>
       </c>
       <c r="W2" t="n">
-        <v>279412000</v>
+        <v>1200590000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>279412000</v>
+        <v>1200590000</v>
       </c>
       <c r="Z2" t="n">
-        <v>65197000</v>
+        <v>-80932000</v>
       </c>
       <c r="AA2" t="n">
-        <v>214215000</v>
+        <v>1281522000</v>
       </c>
       <c r="AB2" t="n">
-        <v>214215000</v>
+        <v>1281522000</v>
       </c>
       <c r="AC2" t="n">
-        <v>264486000</v>
+        <v>171581000</v>
       </c>
       <c r="AD2" t="n">
-        <v>478701000</v>
+        <v>1453103000</v>
       </c>
       <c r="AE2" t="n">
-        <v>242093000</v>
+        <v>12479000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-614376000</v>
+        <v>71000</v>
       </c>
       <c r="AG2" t="n">
-        <v>53776000</v>
+        <v>2748000</v>
       </c>
       <c r="AH2" t="n">
-        <v>23178000</v>
+        <v>-2819000</v>
       </c>
       <c r="AI2" t="n">
-        <v>463079000</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>498025000</v>
+        <v>-908708000</v>
       </c>
       <c r="AK2" t="n">
-        <v>922872000</v>
+        <v>1001454000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1420897000</v>
+        <v>92746000</v>
       </c>
       <c r="AM2" t="n">
-        <v>600502000</v>
+        <v>2212733000</v>
       </c>
       <c r="AN2" t="n">
-        <v>746097000</v>
+        <v>1021092000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-85684000</v>
+        <v>-269384000</v>
       </c>
       <c r="AP2" t="n">
-        <v>907365000</v>
+        <v>1333345000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>147981000</v>
+        <v>416311000</v>
       </c>
       <c r="AR2" t="n">
-        <v>759384000</v>
+        <v>917034000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1346599000</v>
+        <v>3233825000</v>
       </c>
       <c r="AT2" t="n">
-        <v>4770426000</v>
+        <v>9482950000</v>
       </c>
       <c r="AU2" t="n">
-        <v>6117025000</v>
+        <v>12716775000</v>
       </c>
       <c r="AV2" t="n">
-        <v>6117025000</v>
+        <v>12716775000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-2045783.296471</v>
+        <v>-9335790.764749</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009995</v>
+        <v>0.216021</v>
       </c>
       <c r="D3" t="n">
-        <v>1481789000</v>
+        <v>2945048000</v>
       </c>
       <c r="E3" t="n">
-        <v>-5294000</v>
+        <v>-26593000</v>
       </c>
       <c r="F3" t="n">
-        <v>-204682000</v>
+        <v>-43217000</v>
       </c>
       <c r="G3" t="n">
-        <v>-633875000</v>
+        <v>448690000</v>
       </c>
       <c r="H3" t="n">
-        <v>954261000</v>
+        <v>1197181000</v>
       </c>
       <c r="I3" t="n">
-        <v>6259487000</v>
+        <v>8341595000</v>
       </c>
       <c r="J3" t="n">
-        <v>1476495000</v>
+        <v>2918455000</v>
       </c>
       <c r="K3" t="n">
-        <v>522234000</v>
+        <v>1721274000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1048568000</v>
+        <v>-938943000</v>
       </c>
       <c r="M3" t="n">
-        <v>1152053000</v>
+        <v>1033388000</v>
       </c>
       <c r="N3" t="n">
-        <v>103485000</v>
+        <v>94445000</v>
       </c>
       <c r="O3" t="n">
-        <v>-231850783.296471</v>
+        <v>499195209.235251</v>
       </c>
       <c r="P3" t="n">
-        <v>-633875000</v>
+        <v>448690000</v>
       </c>
       <c r="Q3" t="n">
-        <v>7245868000</v>
+        <v>9315502000</v>
       </c>
       <c r="R3" t="n">
         <v>2938282000</v>
@@ -863,144 +865,144 @@
         <v>2938282000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.22</v>
+        <v>0.15</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.22</v>
+        <v>0.15</v>
       </c>
       <c r="V3" t="n">
-        <v>-633875000</v>
+        <v>448690000</v>
       </c>
       <c r="W3" t="n">
-        <v>-633875000</v>
+        <v>448690000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-633875000</v>
+        <v>448690000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-10351000</v>
+        <v>-90598000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-623524000</v>
+        <v>539288000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-623524000</v>
+        <v>539288000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-6295000</v>
+        <v>148598000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-629819000</v>
+        <v>687886000</v>
       </c>
       <c r="AE3" t="n">
-        <v>56083000</v>
+        <v>106295000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-202434000</v>
+        <v>-42933000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-7301000</v>
+        <v>168000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-5005000</v>
+        <v>-1235000</v>
       </c>
       <c r="AI3" t="n">
-        <v>15352000</v>
+        <v>27376000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1048568000</v>
+        <v>-938943000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1152053000</v>
+        <v>1033388000</v>
       </c>
       <c r="AL3" t="n">
-        <v>103485000</v>
+        <v>94445000</v>
       </c>
       <c r="AM3" t="n">
-        <v>642942000</v>
+        <v>1739937000</v>
       </c>
       <c r="AN3" t="n">
-        <v>986381000</v>
+        <v>973907000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-112207000</v>
+        <v>-173390000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1145263000</v>
+        <v>1194900000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>239672000</v>
+        <v>240617000</v>
       </c>
       <c r="AR3" t="n">
-        <v>905591000</v>
+        <v>954283000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1629323000</v>
+        <v>2713844000</v>
       </c>
       <c r="AT3" t="n">
-        <v>6259487000</v>
+        <v>8341595000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7888810000</v>
+        <v>11055439000</v>
       </c>
       <c r="AV3" t="n">
-        <v>7888810000</v>
+        <v>11055439000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-9335790.764749</v>
+        <v>-2045783.296471</v>
       </c>
       <c r="C4" t="n">
-        <v>0.216021</v>
+        <v>0.009995</v>
       </c>
       <c r="D4" t="n">
-        <v>2945048000</v>
+        <v>1481789000</v>
       </c>
       <c r="E4" t="n">
-        <v>-26593000</v>
+        <v>-5294000</v>
       </c>
       <c r="F4" t="n">
-        <v>-43217000</v>
+        <v>-204682000</v>
       </c>
       <c r="G4" t="n">
-        <v>448690000</v>
+        <v>-633875000</v>
       </c>
       <c r="H4" t="n">
-        <v>1197181000</v>
+        <v>954261000</v>
       </c>
       <c r="I4" t="n">
-        <v>8341595000</v>
+        <v>6259487000</v>
       </c>
       <c r="J4" t="n">
-        <v>2918455000</v>
+        <v>1476495000</v>
       </c>
       <c r="K4" t="n">
-        <v>1721274000</v>
+        <v>522234000</v>
       </c>
       <c r="L4" t="n">
-        <v>-938943000</v>
+        <v>-1048568000</v>
       </c>
       <c r="M4" t="n">
-        <v>1033388000</v>
+        <v>1152053000</v>
       </c>
       <c r="N4" t="n">
-        <v>94445000</v>
+        <v>103485000</v>
       </c>
       <c r="O4" t="n">
-        <v>499195209.235251</v>
+        <v>-231850783.296471</v>
       </c>
       <c r="P4" t="n">
-        <v>448690000</v>
+        <v>-633875000</v>
       </c>
       <c r="Q4" t="n">
-        <v>9315502000</v>
+        <v>7245868000</v>
       </c>
       <c r="R4" t="n">
         <v>2938282000</v>
@@ -1009,144 +1011,144 @@
         <v>2938282000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0.15</v>
+        <v>-0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>448690000</v>
+        <v>-633875000</v>
       </c>
       <c r="W4" t="n">
-        <v>448690000</v>
+        <v>-633875000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>448690000</v>
+        <v>-633875000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-90598000</v>
+        <v>-10351000</v>
       </c>
       <c r="AA4" t="n">
-        <v>539288000</v>
+        <v>-623524000</v>
       </c>
       <c r="AB4" t="n">
-        <v>539288000</v>
+        <v>-623524000</v>
       </c>
       <c r="AC4" t="n">
-        <v>148598000</v>
+        <v>-6295000</v>
       </c>
       <c r="AD4" t="n">
-        <v>687886000</v>
+        <v>-629819000</v>
       </c>
       <c r="AE4" t="n">
-        <v>106295000</v>
+        <v>56083000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-42933000</v>
+        <v>-202434000</v>
       </c>
       <c r="AG4" t="n">
-        <v>168000</v>
+        <v>-7301000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1235000</v>
+        <v>-5005000</v>
       </c>
       <c r="AI4" t="n">
-        <v>27376000</v>
+        <v>15352000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-938943000</v>
+        <v>-1048568000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1033388000</v>
+        <v>1152053000</v>
       </c>
       <c r="AL4" t="n">
-        <v>94445000</v>
+        <v>103485000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1739937000</v>
+        <v>642942000</v>
       </c>
       <c r="AN4" t="n">
-        <v>973907000</v>
+        <v>986381000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-173390000</v>
+        <v>-112207000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1194900000</v>
+        <v>1145263000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>240617000</v>
+        <v>239672000</v>
       </c>
       <c r="AR4" t="n">
-        <v>954283000</v>
+        <v>905591000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2713844000</v>
+        <v>1629323000</v>
       </c>
       <c r="AT4" t="n">
-        <v>8341595000</v>
+        <v>6259487000</v>
       </c>
       <c r="AU4" t="n">
-        <v>11055439000</v>
+        <v>7888810000</v>
       </c>
       <c r="AV4" t="n">
-        <v>11055439000</v>
+        <v>7888810000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1557580.550725</v>
+        <v>-151540000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.118079</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>3629965000</v>
+        <v>2789821000</v>
       </c>
       <c r="E5" t="n">
-        <v>13191000</v>
+        <v>-531817000</v>
       </c>
       <c r="F5" t="n">
-        <v>13191000</v>
+        <v>-606160000</v>
       </c>
       <c r="G5" t="n">
-        <v>1200590000</v>
+        <v>279412000</v>
       </c>
       <c r="H5" t="n">
-        <v>1188599000</v>
+        <v>856431000</v>
       </c>
       <c r="I5" t="n">
-        <v>9482950000</v>
+        <v>4770426000</v>
       </c>
       <c r="J5" t="n">
-        <v>3643156000</v>
+        <v>2258004000</v>
       </c>
       <c r="K5" t="n">
-        <v>2454557000</v>
+        <v>1401573000</v>
       </c>
       <c r="L5" t="n">
-        <v>-908708000</v>
+        <v>498025000</v>
       </c>
       <c r="M5" t="n">
-        <v>1001454000</v>
+        <v>922872000</v>
       </c>
       <c r="N5" t="n">
-        <v>92746000</v>
+        <v>1420897000</v>
       </c>
       <c r="O5" t="n">
-        <v>1188956580.550725</v>
+        <v>808375000</v>
       </c>
       <c r="P5" t="n">
-        <v>1200590000</v>
+        <v>279412000</v>
       </c>
       <c r="Q5" t="n">
-        <v>10504042000</v>
+        <v>5516523000</v>
       </c>
       <c r="R5" t="n">
         <v>2938282000</v>
@@ -1155,91 +1157,89 @@
         <v>2938282000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.41</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>1200590000</v>
+        <v>279412000</v>
       </c>
       <c r="W5" t="n">
-        <v>1200590000</v>
+        <v>279412000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1200590000</v>
+        <v>279412000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-80932000</v>
+        <v>65197000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1281522000</v>
+        <v>214215000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1281522000</v>
+        <v>214215000</v>
       </c>
       <c r="AC5" t="n">
-        <v>171581000</v>
+        <v>264486000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1453103000</v>
+        <v>478701000</v>
       </c>
       <c r="AE5" t="n">
-        <v>12479000</v>
+        <v>242093000</v>
       </c>
       <c r="AF5" t="n">
-        <v>71000</v>
+        <v>-614376000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2748000</v>
+        <v>53776000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-2819000</v>
+        <v>23178000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>463079000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-908708000</v>
+        <v>498025000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1001454000</v>
+        <v>922872000</v>
       </c>
       <c r="AL5" t="n">
-        <v>92746000</v>
+        <v>1420897000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2212733000</v>
+        <v>600502000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1021092000</v>
+        <v>746097000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-269384000</v>
+        <v>-85684000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1333345000</v>
+        <v>907365000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>416311000</v>
+        <v>147981000</v>
       </c>
       <c r="AR5" t="n">
-        <v>917034000</v>
+        <v>759384000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3233825000</v>
+        <v>1346599000</v>
       </c>
       <c r="AT5" t="n">
-        <v>9482950000</v>
+        <v>4770426000</v>
       </c>
       <c r="AU5" t="n">
-        <v>12716775000</v>
+        <v>6117025000</v>
       </c>
       <c r="AV5" t="n">
-        <v>12716775000</v>
+        <v>6117025000</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>2938281647</v>
@@ -1629,46 +1629,44 @@
         <v>2938281647</v>
       </c>
       <c r="D2" t="n">
-        <v>11927521000</v>
+        <v>7146201000</v>
       </c>
       <c r="E2" t="n">
-        <v>12843933000</v>
+        <v>9475568000</v>
       </c>
       <c r="F2" t="n">
-        <v>14897717000</v>
+        <v>14572137000</v>
       </c>
       <c r="G2" t="n">
-        <v>28579601000</v>
+        <v>25340440000</v>
       </c>
       <c r="H2" t="n">
-        <v>6959051000</v>
+        <v>3670806000</v>
       </c>
       <c r="I2" t="n">
-        <v>14897717000</v>
+        <v>14572137000</v>
       </c>
       <c r="J2" t="n">
-        <v>1320000</v>
+        <v>18736000</v>
       </c>
       <c r="K2" t="n">
-        <v>15736988000</v>
+        <v>15883608000</v>
       </c>
       <c r="L2" t="n">
-        <v>17420281000</v>
+        <v>18232787000</v>
       </c>
       <c r="M2" t="n">
-        <v>15975507000</v>
+        <v>16068278000</v>
       </c>
       <c r="N2" t="n">
-        <v>238519000</v>
+        <v>184670000</v>
       </c>
       <c r="O2" t="n">
-        <v>15736988000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>31768000</v>
-      </c>
+        <v>15883608000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>11152227000</v>
+        <v>11340755000</v>
       </c>
       <c r="R2" t="n">
         <v>1066648000</v>
@@ -1680,164 +1678,168 @@
         <v>24183000</v>
       </c>
       <c r="U2" t="n">
-        <v>21239599000</v>
+        <v>16589957000</v>
       </c>
       <c r="V2" t="n">
-        <v>2314593000</v>
+        <v>3334997000</v>
       </c>
       <c r="W2" t="n">
-        <v>285951000</v>
+        <v>343361000</v>
       </c>
       <c r="X2" t="n">
-        <v>104989000</v>
+        <v>209460000</v>
       </c>
       <c r="Y2" t="n">
-        <v>169239000</v>
+        <v>167217000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1683717000</v>
+        <v>2355787000</v>
       </c>
       <c r="AA2" t="n">
-        <v>424000</v>
+        <v>6608000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1683293000</v>
+        <v>2349179000</v>
       </c>
       <c r="AC2" t="n">
-        <v>70697000</v>
+        <v>43422000</v>
       </c>
       <c r="AD2" t="n">
-        <v>18925006000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>13254960000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>93969000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>592197000</v>
+        <v>331676000</v>
       </c>
       <c r="AG2" t="n">
-        <v>11160216000</v>
+        <v>7119781000</v>
       </c>
       <c r="AH2" t="n">
-        <v>896000</v>
+        <v>12128000</v>
       </c>
       <c r="AI2" t="n">
-        <v>11159320000</v>
+        <v>7107653000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5579792000</v>
+        <v>4273572000</v>
       </c>
       <c r="AK2" t="n">
-        <v>839605000</v>
+        <v>744688000</v>
       </c>
       <c r="AL2" t="n">
-        <v>75507000</v>
+        <v>130864000</v>
       </c>
       <c r="AM2" t="n">
-        <v>4664680000</v>
+        <v>3398020000</v>
       </c>
       <c r="AN2" t="n">
-        <v>37215106000</v>
+        <v>32658235000</v>
       </c>
       <c r="AO2" t="n">
-        <v>11331049000</v>
+        <v>15732469000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>933880000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>186423000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>155771000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1155000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>796271000</v>
+        <v>1111346000</v>
       </c>
       <c r="AT2" t="n">
-        <v>796271000</v>
+        <v>1111346000</v>
       </c>
       <c r="AU2" t="n">
-        <v>839271000</v>
+        <v>1311471000</v>
       </c>
       <c r="AV2" t="n">
-        <v>828769000</v>
+        <v>1010614000</v>
       </c>
       <c r="AW2" t="n">
-        <v>10502000</v>
+        <v>300857000</v>
       </c>
       <c r="AX2" t="n">
-        <v>9500104000</v>
+        <v>11652892000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-13324328000</v>
+        <v>-10352361000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22824432000</v>
+        <v>22005253000</v>
       </c>
       <c r="BA2" t="n">
-        <v>152545000</v>
+        <v>434107000</v>
       </c>
       <c r="BB2" t="n">
-        <v>1997761000</v>
+        <v>2013607000</v>
       </c>
       <c r="BC2" t="n">
-        <v>9315573000</v>
+        <v>8899649000</v>
       </c>
       <c r="BD2" t="n">
-        <v>9108931000</v>
+        <v>8911751000</v>
       </c>
       <c r="BE2" t="n">
-        <v>2249622000</v>
+        <v>1746139000</v>
       </c>
       <c r="BF2" t="n">
-        <v>25884057000</v>
+        <v>16925766000</v>
       </c>
       <c r="BG2" t="n">
-        <v>2304761000</v>
+        <v>4369881000</v>
       </c>
       <c r="BH2" t="n">
-        <v>15157039000</v>
+        <v>2696332000</v>
       </c>
       <c r="BI2" t="n">
-        <v>675668000</v>
+        <v>850721000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>328939000</v>
+        <v>328927000</v>
       </c>
       <c r="BK2" t="n">
-        <v>20015000</v>
+        <v>4772000</v>
       </c>
       <c r="BL2" t="n">
-        <v>326714000</v>
+        <v>517022000</v>
       </c>
       <c r="BM2" t="n">
-        <v>6693145000</v>
+        <v>6508307000</v>
       </c>
       <c r="BN2" t="n">
-        <v>131473000</v>
+        <v>180200000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-35492000</v>
+        <v>-54597000</v>
       </c>
       <c r="BP2" t="n">
-        <v>166965000</v>
+        <v>234797000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>921971000</v>
+        <v>2320325000</v>
       </c>
       <c r="BR2" t="n">
-        <v>6879000</v>
+        <v>9694000</v>
       </c>
       <c r="BS2" t="n">
-        <v>915092000</v>
+        <v>2310631000</v>
       </c>
       <c r="BT2" t="n">
-        <v>811489000</v>
+        <v>1128047000</v>
       </c>
       <c r="BU2" t="n">
-        <v>103603000</v>
+        <v>1182584000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>2938281647</v>
@@ -1846,46 +1848,46 @@
         <v>2938281647</v>
       </c>
       <c r="D3" t="n">
-        <v>16537653000</v>
+        <v>7459135000</v>
       </c>
       <c r="E3" t="n">
-        <v>17720338000</v>
+        <v>8456129000</v>
       </c>
       <c r="F3" t="n">
-        <v>14337480000</v>
+        <v>15032717000</v>
       </c>
       <c r="G3" t="n">
-        <v>33178930000</v>
+        <v>24761758000</v>
       </c>
       <c r="H3" t="n">
-        <v>8512709000</v>
+        <v>3352372000</v>
       </c>
       <c r="I3" t="n">
-        <v>14337480000</v>
+        <v>15032717000</v>
       </c>
       <c r="J3" t="n">
-        <v>7844000</v>
+        <v>9197000</v>
       </c>
       <c r="K3" t="n">
-        <v>15466436000</v>
+        <v>16314826000</v>
       </c>
       <c r="L3" t="n">
-        <v>20089861000</v>
+        <v>17711841000</v>
       </c>
       <c r="M3" t="n">
-        <v>15786067000</v>
+        <v>16590094000</v>
       </c>
       <c r="N3" t="n">
-        <v>319631000</v>
+        <v>275268000</v>
       </c>
       <c r="O3" t="n">
-        <v>15466436000</v>
+        <v>16314826000</v>
       </c>
       <c r="P3" t="n">
         <v>31768000</v>
       </c>
       <c r="Q3" t="n">
-        <v>10909253000</v>
+        <v>11739129000</v>
       </c>
       <c r="R3" t="n">
         <v>1066648000</v>
@@ -1897,166 +1899,166 @@
         <v>24183000</v>
       </c>
       <c r="U3" t="n">
-        <v>24787427000</v>
+        <v>15753498000</v>
       </c>
       <c r="V3" t="n">
-        <v>5973210000</v>
+        <v>2231768000</v>
       </c>
       <c r="W3" t="n">
-        <v>358073000</v>
+        <v>423093000</v>
       </c>
       <c r="X3" t="n">
-        <v>175372000</v>
+        <v>192416000</v>
       </c>
       <c r="Y3" t="n">
-        <v>154975000</v>
+        <v>159218000</v>
       </c>
       <c r="Z3" t="n">
-        <v>4629089000</v>
+        <v>1402633000</v>
       </c>
       <c r="AA3" t="n">
-        <v>5664000</v>
+        <v>5618000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4623425000</v>
+        <v>1397015000</v>
       </c>
       <c r="AC3" t="n">
-        <v>45811000</v>
+        <v>54408000</v>
       </c>
       <c r="AD3" t="n">
-        <v>18814217000</v>
+        <v>13521730000</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>270485000</v>
+        <v>302362000</v>
       </c>
       <c r="AG3" t="n">
-        <v>13091249000</v>
+        <v>7053496000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2180000</v>
+        <v>3579000</v>
       </c>
       <c r="AI3" t="n">
-        <v>13089069000</v>
+        <v>7049917000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4707418000</v>
+        <v>4403336000</v>
       </c>
       <c r="AK3" t="n">
-        <v>407126000</v>
+        <v>610982000</v>
       </c>
       <c r="AL3" t="n">
-        <v>34971000</v>
+        <v>130665000</v>
       </c>
       <c r="AM3" t="n">
-        <v>4265321000</v>
+        <v>3661689000</v>
       </c>
       <c r="AN3" t="n">
-        <v>40573494000</v>
+        <v>32343592000</v>
       </c>
       <c r="AO3" t="n">
-        <v>13246568000</v>
+        <v>15469490000</v>
       </c>
       <c r="AP3" t="n">
-        <v>116480000</v>
+        <v>1037153000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>104811000</v>
+        <v>109613000</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>495000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1004269000</v>
+        <v>1086802000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1004269000</v>
+        <v>1086802000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1128956000</v>
+        <v>1282109000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1044111000</v>
+        <v>997876000</v>
       </c>
       <c r="AW3" t="n">
-        <v>84845000</v>
+        <v>284233000</v>
       </c>
       <c r="AX3" t="n">
-        <v>10876263000</v>
+        <v>11497791000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-12370377000</v>
+        <v>-11488839000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23246640000</v>
+        <v>22986630000</v>
       </c>
       <c r="BA3" t="n">
-        <v>403500000</v>
+        <v>569835000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1966955000</v>
+        <v>1951133000</v>
       </c>
       <c r="BC3" t="n">
-        <v>9385591000</v>
+        <v>9286963000</v>
       </c>
       <c r="BD3" t="n">
-        <v>9366025000</v>
+        <v>9220900000</v>
       </c>
       <c r="BE3" t="n">
-        <v>2124569000</v>
+        <v>1957799000</v>
       </c>
       <c r="BF3" t="n">
-        <v>27326926000</v>
+        <v>16874102000</v>
       </c>
       <c r="BG3" t="n">
-        <v>5118386000</v>
+        <v>4546923000</v>
       </c>
       <c r="BH3" t="n">
-        <v>14403576000</v>
+        <v>5649494000</v>
       </c>
       <c r="BI3" t="n">
-        <v>819126000</v>
+        <v>1042962000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>410284000</v>
+        <v>454525000</v>
       </c>
       <c r="BK3" t="n">
-        <v>9598000</v>
+        <v>23865000</v>
       </c>
       <c r="BL3" t="n">
-        <v>399244000</v>
+        <v>564572000</v>
       </c>
       <c r="BM3" t="n">
-        <v>5655207000</v>
+        <v>4498664000</v>
       </c>
       <c r="BN3" t="n">
-        <v>142705000</v>
+        <v>109361000</v>
       </c>
       <c r="BO3" t="n">
-        <v>-43202000</v>
+        <v>-50238000</v>
       </c>
       <c r="BP3" t="n">
-        <v>185907000</v>
+        <v>159599000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1187926000</v>
+        <v>1026698000</v>
       </c>
       <c r="BR3" t="n">
-        <v>13085000</v>
+        <v>38901000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1174841000</v>
+        <v>987797000</v>
       </c>
       <c r="BT3" t="n">
-        <v>1049034000</v>
+        <v>386076000</v>
       </c>
       <c r="BU3" t="n">
-        <v>125807000</v>
+        <v>601721000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>2938281647</v>
@@ -2065,46 +2067,46 @@
         <v>2938281647</v>
       </c>
       <c r="D4" t="n">
-        <v>7459135000</v>
+        <v>16537653000</v>
       </c>
       <c r="E4" t="n">
-        <v>8456129000</v>
+        <v>17720338000</v>
       </c>
       <c r="F4" t="n">
-        <v>15032717000</v>
+        <v>14337480000</v>
       </c>
       <c r="G4" t="n">
-        <v>24761758000</v>
+        <v>33178930000</v>
       </c>
       <c r="H4" t="n">
-        <v>3352372000</v>
+        <v>8512709000</v>
       </c>
       <c r="I4" t="n">
-        <v>15032717000</v>
+        <v>14337480000</v>
       </c>
       <c r="J4" t="n">
-        <v>9197000</v>
+        <v>7844000</v>
       </c>
       <c r="K4" t="n">
-        <v>16314826000</v>
+        <v>15466436000</v>
       </c>
       <c r="L4" t="n">
-        <v>17711841000</v>
+        <v>20089861000</v>
       </c>
       <c r="M4" t="n">
-        <v>16590094000</v>
+        <v>15786067000</v>
       </c>
       <c r="N4" t="n">
-        <v>275268000</v>
+        <v>319631000</v>
       </c>
       <c r="O4" t="n">
-        <v>16314826000</v>
+        <v>15466436000</v>
       </c>
       <c r="P4" t="n">
         <v>31768000</v>
       </c>
       <c r="Q4" t="n">
-        <v>11739129000</v>
+        <v>10909253000</v>
       </c>
       <c r="R4" t="n">
         <v>1066648000</v>
@@ -2116,166 +2118,166 @@
         <v>24183000</v>
       </c>
       <c r="U4" t="n">
-        <v>15753498000</v>
+        <v>24787427000</v>
       </c>
       <c r="V4" t="n">
-        <v>2231768000</v>
+        <v>5973210000</v>
       </c>
       <c r="W4" t="n">
-        <v>423093000</v>
+        <v>358073000</v>
       </c>
       <c r="X4" t="n">
-        <v>192416000</v>
+        <v>175372000</v>
       </c>
       <c r="Y4" t="n">
-        <v>159218000</v>
+        <v>154975000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1402633000</v>
+        <v>4629089000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5618000</v>
+        <v>5664000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1397015000</v>
+        <v>4623425000</v>
       </c>
       <c r="AC4" t="n">
-        <v>54408000</v>
+        <v>45811000</v>
       </c>
       <c r="AD4" t="n">
-        <v>13521730000</v>
+        <v>18814217000</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>302362000</v>
+        <v>270485000</v>
       </c>
       <c r="AG4" t="n">
-        <v>7053496000</v>
+        <v>13091249000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3579000</v>
+        <v>2180000</v>
       </c>
       <c r="AI4" t="n">
-        <v>7049917000</v>
+        <v>13089069000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4403336000</v>
+        <v>4707418000</v>
       </c>
       <c r="AK4" t="n">
-        <v>610982000</v>
+        <v>407126000</v>
       </c>
       <c r="AL4" t="n">
-        <v>130665000</v>
+        <v>34971000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3661689000</v>
+        <v>4265321000</v>
       </c>
       <c r="AN4" t="n">
-        <v>32343592000</v>
+        <v>40573494000</v>
       </c>
       <c r="AO4" t="n">
-        <v>15469490000</v>
+        <v>13246568000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1037153000</v>
+        <v>116480000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>109613000</v>
+        <v>104811000</v>
       </c>
       <c r="AR4" t="n">
-        <v>495000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>1086802000</v>
+        <v>1004269000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1086802000</v>
+        <v>1004269000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1282109000</v>
+        <v>1128956000</v>
       </c>
       <c r="AV4" t="n">
-        <v>997876000</v>
+        <v>1044111000</v>
       </c>
       <c r="AW4" t="n">
-        <v>284233000</v>
+        <v>84845000</v>
       </c>
       <c r="AX4" t="n">
-        <v>11497791000</v>
+        <v>10876263000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-11488839000</v>
+        <v>-12370377000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22986630000</v>
+        <v>23246640000</v>
       </c>
       <c r="BA4" t="n">
-        <v>569835000</v>
+        <v>403500000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1951133000</v>
+        <v>1966955000</v>
       </c>
       <c r="BC4" t="n">
-        <v>9286963000</v>
+        <v>9385591000</v>
       </c>
       <c r="BD4" t="n">
-        <v>9220900000</v>
+        <v>9366025000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1957799000</v>
+        <v>2124569000</v>
       </c>
       <c r="BF4" t="n">
-        <v>16874102000</v>
+        <v>27326926000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4546923000</v>
+        <v>5118386000</v>
       </c>
       <c r="BH4" t="n">
-        <v>5649494000</v>
+        <v>14403576000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1042962000</v>
+        <v>819126000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>454525000</v>
+        <v>410284000</v>
       </c>
       <c r="BK4" t="n">
-        <v>23865000</v>
+        <v>9598000</v>
       </c>
       <c r="BL4" t="n">
-        <v>564572000</v>
+        <v>399244000</v>
       </c>
       <c r="BM4" t="n">
-        <v>4498664000</v>
+        <v>5655207000</v>
       </c>
       <c r="BN4" t="n">
-        <v>109361000</v>
+        <v>142705000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-50238000</v>
+        <v>-43202000</v>
       </c>
       <c r="BP4" t="n">
-        <v>159599000</v>
+        <v>185907000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1026698000</v>
+        <v>1187926000</v>
       </c>
       <c r="BR4" t="n">
-        <v>38901000</v>
+        <v>13085000</v>
       </c>
       <c r="BS4" t="n">
-        <v>987797000</v>
+        <v>1174841000</v>
       </c>
       <c r="BT4" t="n">
-        <v>386076000</v>
+        <v>1049034000</v>
       </c>
       <c r="BU4" t="n">
-        <v>601721000</v>
+        <v>125807000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>2938281647</v>
@@ -2284,44 +2286,46 @@
         <v>2938281647</v>
       </c>
       <c r="D5" t="n">
-        <v>7146201000</v>
+        <v>11927521000</v>
       </c>
       <c r="E5" t="n">
-        <v>9475568000</v>
+        <v>12843933000</v>
       </c>
       <c r="F5" t="n">
-        <v>14572137000</v>
+        <v>14897717000</v>
       </c>
       <c r="G5" t="n">
-        <v>25340440000</v>
+        <v>28579601000</v>
       </c>
       <c r="H5" t="n">
-        <v>3670806000</v>
+        <v>6959051000</v>
       </c>
       <c r="I5" t="n">
-        <v>14572137000</v>
+        <v>14897717000</v>
       </c>
       <c r="J5" t="n">
-        <v>18736000</v>
+        <v>1320000</v>
       </c>
       <c r="K5" t="n">
-        <v>15883608000</v>
+        <v>15736988000</v>
       </c>
       <c r="L5" t="n">
-        <v>18232787000</v>
+        <v>17420281000</v>
       </c>
       <c r="M5" t="n">
-        <v>16068278000</v>
+        <v>15975507000</v>
       </c>
       <c r="N5" t="n">
-        <v>184670000</v>
+        <v>238519000</v>
       </c>
       <c r="O5" t="n">
-        <v>15883608000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>15736988000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>31768000</v>
+      </c>
       <c r="Q5" t="n">
-        <v>11340755000</v>
+        <v>11152227000</v>
       </c>
       <c r="R5" t="n">
         <v>1066648000</v>
@@ -2333,163 +2337,159 @@
         <v>24183000</v>
       </c>
       <c r="U5" t="n">
-        <v>16589957000</v>
+        <v>21239599000</v>
       </c>
       <c r="V5" t="n">
-        <v>3334997000</v>
+        <v>2314593000</v>
       </c>
       <c r="W5" t="n">
-        <v>343361000</v>
+        <v>285951000</v>
       </c>
       <c r="X5" t="n">
-        <v>209460000</v>
+        <v>104989000</v>
       </c>
       <c r="Y5" t="n">
-        <v>167217000</v>
+        <v>169239000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2355787000</v>
+        <v>1683717000</v>
       </c>
       <c r="AA5" t="n">
-        <v>6608000</v>
+        <v>424000</v>
       </c>
       <c r="AB5" t="n">
-        <v>2349179000</v>
+        <v>1683293000</v>
       </c>
       <c r="AC5" t="n">
-        <v>43422000</v>
+        <v>70697000</v>
       </c>
       <c r="AD5" t="n">
-        <v>13254960000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>93969000</v>
-      </c>
+        <v>18925006000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>331676000</v>
+        <v>592197000</v>
       </c>
       <c r="AG5" t="n">
-        <v>7119781000</v>
+        <v>11160216000</v>
       </c>
       <c r="AH5" t="n">
-        <v>12128000</v>
+        <v>896000</v>
       </c>
       <c r="AI5" t="n">
-        <v>7107653000</v>
+        <v>11159320000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4273572000</v>
+        <v>5579792000</v>
       </c>
       <c r="AK5" t="n">
-        <v>744688000</v>
+        <v>839605000</v>
       </c>
       <c r="AL5" t="n">
-        <v>130864000</v>
+        <v>75507000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3398020000</v>
+        <v>4664680000</v>
       </c>
       <c r="AN5" t="n">
-        <v>32658235000</v>
+        <v>37215106000</v>
       </c>
       <c r="AO5" t="n">
-        <v>15732469000</v>
+        <v>11331049000</v>
       </c>
       <c r="AP5" t="n">
-        <v>933880000</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>155771000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1155000</v>
-      </c>
+        <v>186423000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>1111346000</v>
+        <v>796271000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1111346000</v>
+        <v>796271000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1311471000</v>
+        <v>839271000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1010614000</v>
+        <v>828769000</v>
       </c>
       <c r="AW5" t="n">
-        <v>300857000</v>
+        <v>10502000</v>
       </c>
       <c r="AX5" t="n">
-        <v>11652892000</v>
+        <v>9500104000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-10352361000</v>
+        <v>-13324328000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22005253000</v>
+        <v>22824432000</v>
       </c>
       <c r="BA5" t="n">
-        <v>434107000</v>
+        <v>152545000</v>
       </c>
       <c r="BB5" t="n">
-        <v>2013607000</v>
+        <v>1997761000</v>
       </c>
       <c r="BC5" t="n">
-        <v>8899649000</v>
+        <v>9315573000</v>
       </c>
       <c r="BD5" t="n">
-        <v>8911751000</v>
+        <v>9108931000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1746139000</v>
+        <v>2249622000</v>
       </c>
       <c r="BF5" t="n">
-        <v>16925766000</v>
+        <v>25884057000</v>
       </c>
       <c r="BG5" t="n">
-        <v>4369881000</v>
+        <v>2304761000</v>
       </c>
       <c r="BH5" t="n">
-        <v>2696332000</v>
+        <v>15157039000</v>
       </c>
       <c r="BI5" t="n">
-        <v>850721000</v>
+        <v>675668000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>328927000</v>
+        <v>328939000</v>
       </c>
       <c r="BK5" t="n">
-        <v>4772000</v>
+        <v>20015000</v>
       </c>
       <c r="BL5" t="n">
-        <v>517022000</v>
+        <v>326714000</v>
       </c>
       <c r="BM5" t="n">
-        <v>6508307000</v>
+        <v>6693145000</v>
       </c>
       <c r="BN5" t="n">
-        <v>180200000</v>
+        <v>131473000</v>
       </c>
       <c r="BO5" t="n">
-        <v>-54597000</v>
+        <v>-35492000</v>
       </c>
       <c r="BP5" t="n">
-        <v>234797000</v>
+        <v>166965000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2320325000</v>
+        <v>921971000</v>
       </c>
       <c r="BR5" t="n">
-        <v>9694000</v>
+        <v>6879000</v>
       </c>
       <c r="BS5" t="n">
-        <v>2310631000</v>
+        <v>915092000</v>
       </c>
       <c r="BT5" t="n">
-        <v>1128047000</v>
+        <v>811489000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1182584000</v>
+        <v>103603000</v>
       </c>
     </row>
   </sheetData>
@@ -2755,570 +2755,570 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1175606000</v>
+        <v>2330150000</v>
       </c>
       <c r="C2" t="n">
-        <v>-14536463000</v>
+        <v>-20384525000</v>
       </c>
       <c r="D2" t="n">
-        <v>10365654000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42325000</v>
-      </c>
+        <v>19683964000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-374933000</v>
+        <v>-400259000</v>
       </c>
       <c r="G2" t="n">
-        <v>915092000</v>
+        <v>2310631000</v>
       </c>
       <c r="H2" t="n">
-        <v>1174841000</v>
+        <v>2412115000</v>
       </c>
       <c r="I2" t="n">
-        <v>-259749000</v>
+        <v>-101484000</v>
       </c>
       <c r="J2" t="n">
-        <v>-4896029000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-5000000</v>
-      </c>
+        <v>-1647787000</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-761516000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>42325000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>42325000</v>
-      </c>
+        <v>-894286000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-25110000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-4170809000</v>
+        <v>-700561000</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-4170809000</v>
+        <v>-700561000</v>
       </c>
       <c r="T2" t="n">
-        <v>-14536463000</v>
+        <v>-20384525000</v>
       </c>
       <c r="U2" t="n">
-        <v>10365654000</v>
+        <v>19683964000</v>
       </c>
       <c r="V2" t="n">
-        <v>3085741000</v>
+        <v>-1184106000</v>
       </c>
       <c r="W2" t="n">
-        <v>2820434000</v>
+        <v>-765380000</v>
       </c>
       <c r="X2" t="n">
-        <v>70692000</v>
+        <v>92746000</v>
       </c>
       <c r="Y2" t="n">
-        <v>14422000</v>
+        <v>5925000</v>
       </c>
       <c r="Z2" t="n">
-        <v>14422000</v>
+        <v>5925000</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>110000</v>
+        <v>-120457000</v>
       </c>
       <c r="AC2" t="n">
-        <v>6120597000</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-6120487000</v>
+        <v>-120457000</v>
       </c>
       <c r="AE2" t="n">
-        <v>180083000</v>
+        <v>-396940000</v>
       </c>
       <c r="AF2" t="n">
-        <v>555016000</v>
+        <v>3319000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-374933000</v>
+        <v>-400259000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1550539000</v>
+        <v>2730409000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-10122000</v>
+        <v>-376993000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-67018000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-286049000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>77603000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>164558000</v>
+        <v>158650000</v>
       </c>
       <c r="AM2" t="n">
-        <v>824783000</v>
+        <v>-543378000</v>
       </c>
       <c r="AN2" t="n">
-        <v>143458000</v>
+        <v>190049000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1199817000</v>
+        <v>-168973000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-594811000</v>
+        <v>884142000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>34233000</v>
+        <v>47608000</v>
       </c>
       <c r="AR2" t="n">
-        <v>856431000</v>
+        <v>1188599000</v>
       </c>
       <c r="AS2" t="n">
-        <v>101773000</v>
+        <v>86039000</v>
       </c>
       <c r="AT2" t="n">
-        <v>754658000</v>
+        <v>1102560000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-8216000</v>
+        <v>-13120000</v>
       </c>
       <c r="AV2" t="n">
-        <v>47270000</v>
+        <v>-88351000</v>
       </c>
       <c r="AW2" t="n">
-        <v>54329000</v>
+        <v>2748000</v>
       </c>
       <c r="AX2" t="n">
-        <v>478701000</v>
+        <v>1453103000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-4762353000</v>
+        <v>3740743000</v>
       </c>
       <c r="C3" t="n">
-        <v>-18879255000</v>
+        <v>-14145803000</v>
       </c>
       <c r="D3" t="n">
-        <v>22427109000</v>
+        <v>12827556000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-540961000</v>
+        <v>-974936000</v>
       </c>
       <c r="G3" t="n">
-        <v>1174841000</v>
+        <v>987797000</v>
       </c>
       <c r="H3" t="n">
-        <v>987797000</v>
+        <v>2310631000</v>
       </c>
       <c r="I3" t="n">
-        <v>187044000</v>
+        <v>-1322834000</v>
       </c>
       <c r="J3" t="n">
-        <v>2486889000</v>
+        <v>-2363366000</v>
       </c>
       <c r="K3" t="n">
-        <v>-382252000</v>
+        <v>-48609000</v>
       </c>
       <c r="L3" t="n">
-        <v>-673906000</v>
+        <v>-957682000</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>3547854000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+        <v>-1318247000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-4443624000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-4443624000</v>
+      </c>
       <c r="S3" t="n">
-        <v>3547854000</v>
+        <v>3125377000</v>
       </c>
       <c r="T3" t="n">
-        <v>-18879255000</v>
+        <v>-9702179000</v>
       </c>
       <c r="U3" t="n">
-        <v>22427109000</v>
+        <v>12827556000</v>
       </c>
       <c r="V3" t="n">
-        <v>1921547000</v>
+        <v>-3675147000</v>
       </c>
       <c r="W3" t="n">
-        <v>-560720000</v>
+        <v>-156861000</v>
       </c>
       <c r="X3" t="n">
-        <v>103485000</v>
+        <v>94445000</v>
       </c>
       <c r="Y3" t="n">
-        <v>24063000</v>
+        <v>-28831000</v>
       </c>
       <c r="Z3" t="n">
-        <v>27063000</v>
+        <v>109768000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3000000</v>
+        <v>-138599000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2811310000</v>
+        <v>-2682796000</v>
       </c>
       <c r="AC3" t="n">
-        <v>13895270000</v>
+        <v>9001602000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-11083960000</v>
+        <v>-11684398000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-503124000</v>
+        <v>-962328000</v>
       </c>
       <c r="AF3" t="n">
-        <v>37837000</v>
+        <v>12608000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-540961000</v>
+        <v>-974936000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-4221392000</v>
+        <v>4715679000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-25023000</v>
+        <v>-139752000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-5802142000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>1831096000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>114446000</v>
+      </c>
       <c r="AL3" t="n">
-        <v>-126946000</v>
+        <v>44491000</v>
       </c>
       <c r="AM3" t="n">
-        <v>205083000</v>
+        <v>-660032000</v>
       </c>
       <c r="AN3" t="n">
-        <v>223836000</v>
+        <v>-192241000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-6104115000</v>
+        <v>2638878000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1009652000</v>
+        <v>908879000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>26868000</v>
+        <v>37122000</v>
       </c>
       <c r="AR3" t="n">
-        <v>954261000</v>
+        <v>1197181000</v>
       </c>
       <c r="AS3" t="n">
-        <v>97051000</v>
+        <v>91160000</v>
       </c>
       <c r="AT3" t="n">
-        <v>857210000</v>
+        <v>1106021000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2248000</v>
+        <v>284000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-17939000</v>
+        <v>141642000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-7301000</v>
+        <v>168000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-629819000</v>
+        <v>687886000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3740743000</v>
+        <v>-4762353000</v>
       </c>
       <c r="C4" t="n">
-        <v>-14145803000</v>
+        <v>-18879255000</v>
       </c>
       <c r="D4" t="n">
-        <v>12827556000</v>
+        <v>22427109000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-974936000</v>
+        <v>-540961000</v>
       </c>
       <c r="G4" t="n">
+        <v>1174841000</v>
+      </c>
+      <c r="H4" t="n">
         <v>987797000</v>
       </c>
-      <c r="H4" t="n">
-        <v>2310631000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-1322834000</v>
+        <v>187044000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2363366000</v>
+        <v>2486889000</v>
       </c>
       <c r="K4" t="n">
-        <v>-48609000</v>
+        <v>-382252000</v>
       </c>
       <c r="L4" t="n">
-        <v>-957682000</v>
+        <v>-673906000</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>-1318247000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-4443624000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-4443624000</v>
-      </c>
+        <v>3547854000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>3125377000</v>
+        <v>3547854000</v>
       </c>
       <c r="T4" t="n">
-        <v>-9702179000</v>
+        <v>-18879255000</v>
       </c>
       <c r="U4" t="n">
-        <v>12827556000</v>
+        <v>22427109000</v>
       </c>
       <c r="V4" t="n">
-        <v>-3675147000</v>
+        <v>1921547000</v>
       </c>
       <c r="W4" t="n">
-        <v>-156861000</v>
+        <v>-560720000</v>
       </c>
       <c r="X4" t="n">
-        <v>94445000</v>
+        <v>103485000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-28831000</v>
+        <v>24063000</v>
       </c>
       <c r="Z4" t="n">
-        <v>109768000</v>
+        <v>27063000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-138599000</v>
+        <v>-3000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2682796000</v>
+        <v>2811310000</v>
       </c>
       <c r="AC4" t="n">
-        <v>9001602000</v>
+        <v>13895270000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-11684398000</v>
+        <v>-11083960000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-962328000</v>
+        <v>-503124000</v>
       </c>
       <c r="AF4" t="n">
-        <v>12608000</v>
+        <v>37837000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-974936000</v>
+        <v>-540961000</v>
       </c>
       <c r="AH4" t="n">
-        <v>4715679000</v>
+        <v>-4221392000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-139752000</v>
+        <v>-25023000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1831096000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>114446000</v>
-      </c>
+        <v>-5802142000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>44491000</v>
+        <v>-126946000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-660032000</v>
+        <v>205083000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-192241000</v>
+        <v>223836000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2638878000</v>
+        <v>-6104115000</v>
       </c>
       <c r="AP4" t="n">
-        <v>908879000</v>
+        <v>1009652000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>37122000</v>
+        <v>26868000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1197181000</v>
+        <v>954261000</v>
       </c>
       <c r="AS4" t="n">
-        <v>91160000</v>
+        <v>97051000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1106021000</v>
+        <v>857210000</v>
       </c>
       <c r="AU4" t="n">
-        <v>284000</v>
+        <v>2248000</v>
       </c>
       <c r="AV4" t="n">
-        <v>141642000</v>
+        <v>-17939000</v>
       </c>
       <c r="AW4" t="n">
-        <v>168000</v>
+        <v>-7301000</v>
       </c>
       <c r="AX4" t="n">
-        <v>687886000</v>
+        <v>-629819000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2330150000</v>
+        <v>1175606000</v>
       </c>
       <c r="C5" t="n">
-        <v>-20384525000</v>
+        <v>-14536463000</v>
       </c>
       <c r="D5" t="n">
-        <v>19683964000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>10365654000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>42325000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-400259000</v>
+        <v>-374933000</v>
       </c>
       <c r="G5" t="n">
-        <v>2310631000</v>
+        <v>915092000</v>
       </c>
       <c r="H5" t="n">
-        <v>2412115000</v>
+        <v>1174841000</v>
       </c>
       <c r="I5" t="n">
-        <v>-101484000</v>
+        <v>-259749000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1647787000</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>-4896029000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-5000000</v>
+      </c>
       <c r="L5" t="n">
-        <v>-894286000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-25110000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>-761516000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>42325000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>42325000</v>
+      </c>
       <c r="P5" t="n">
-        <v>-700561000</v>
+        <v>-4170809000</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-700561000</v>
+        <v>-4170809000</v>
       </c>
       <c r="T5" t="n">
-        <v>-20384525000</v>
+        <v>-14536463000</v>
       </c>
       <c r="U5" t="n">
-        <v>19683964000</v>
+        <v>10365654000</v>
       </c>
       <c r="V5" t="n">
-        <v>-1184106000</v>
+        <v>3085741000</v>
       </c>
       <c r="W5" t="n">
-        <v>-765380000</v>
+        <v>2820434000</v>
       </c>
       <c r="X5" t="n">
-        <v>92746000</v>
+        <v>70692000</v>
       </c>
       <c r="Y5" t="n">
-        <v>5925000</v>
+        <v>14422000</v>
       </c>
       <c r="Z5" t="n">
-        <v>5925000</v>
+        <v>14422000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-120457000</v>
+        <v>110000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6120597000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-120457000</v>
+        <v>-6120487000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-396940000</v>
+        <v>180083000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3319000</v>
+        <v>555016000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-400259000</v>
+        <v>-374933000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2730409000</v>
+        <v>1550539000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-376993000</v>
+        <v>-10122000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-286049000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>77603000</v>
-      </c>
+        <v>-67018000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>158650000</v>
+        <v>164558000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-543378000</v>
+        <v>824783000</v>
       </c>
       <c r="AN5" t="n">
-        <v>190049000</v>
+        <v>143458000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-168973000</v>
+        <v>-1199817000</v>
       </c>
       <c r="AP5" t="n">
-        <v>884142000</v>
+        <v>-594811000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>47608000</v>
+        <v>34233000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1188599000</v>
+        <v>856431000</v>
       </c>
       <c r="AS5" t="n">
-        <v>86039000</v>
+        <v>101773000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1102560000</v>
+        <v>754658000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-13120000</v>
+        <v>-8216000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-88351000</v>
+        <v>47270000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2748000</v>
+        <v>54329000</v>
       </c>
       <c r="AX5" t="n">
-        <v>1453103000</v>
+        <v>478701000</v>
       </c>
     </row>
   </sheetData>
@@ -3868,192 +3868,192 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>epsForward</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Liufa  Li', 'age': 68, 'title': 'Founder &amp; Non-Executive Chairman', 'yearBorn': 1957, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jifeng  Ding', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 566331, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Fengluan  Li', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiangming  Li', 'age': 47, 'title': 'Joint Company Secretary &amp; Executive Director', 'yearBorn': 1978, 'fiscalYear': 2024, 'totalPay': 657825, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tao  Li', 'age': 51, 'title': 'Executive Director', 'yearBorn': 1974, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Mei Ka  Lui', 'age': 40, 'title': 'Joint Company Secretary', 'yearBorn': 1985, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Liufa  Li', 'age': 68, 'title': 'Founder &amp; Non-Executive Chairman', 'yearBorn': 1957, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jifeng  Ding', 'age': 55, 'title': 'Executive Director', 'yearBorn': 1970, 'fiscalYear': 2024, 'totalPay': 566026, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Fengluan  Li', 'age': 62, 'title': 'Executive Director', 'yearBorn': 1963, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiangming  Li', 'age': 47, 'title': 'Joint Company Secretary &amp; Executive Director', 'yearBorn': 1978, 'fiscalYear': 2024, 'totalPay': 657470, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tao  Li', 'age': 51, 'title': 'Executive Director', 'yearBorn': 1974, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Mei Ka  Lui', 'age': 40, 'title': 'Joint Company Secretary', 'yearBorn': 1985, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.772</v>
+        <v>-0.77</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8461539</v>
@@ -4196,7 +4196,7 @@
         <v>98427000</v>
       </c>
       <c r="AI2" t="n">
-        <v>3743850</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -4241,7 +4241,7 @@
         <v>0.24</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.292285</v>
+        <v>0.28056</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>3083281647</v>
       </c>
       <c r="BJ2" t="n">
-        <v>5.95323</v>
+        <v>5.948486</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.04031425</v>
+        <v>0.040346403</v>
       </c>
       <c r="BL2" t="n">
         <v>1735603200</v>
@@ -4312,10 +4312,10 @@
         <v>9.476000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.111111104</v>
+        <v>-0.22580647</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.27</v>
@@ -4432,142 +4432,142 @@
         </is>
       </c>
       <c r="DC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
         <v>0.24</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.040559992</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.14456798</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="inlineStr">
         <is>
           <t>CHINA TIANRUI</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1773994126</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>finmb_33278349</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>China Tianrui Group Cement Company Limited</t>
         </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>1773994126</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>finmb_33278349</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.052285</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.17888363</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>15</v>
       </c>
       <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DY2" t="b">
+      <c r="DY2" t="n">
+        <v>1324603800000</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>0</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>1324603800000</v>
-      </c>
-      <c r="EA2" t="n">
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>0.198 - 0.255</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
         <v>0</v>
       </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>0.198 - 0.255</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
       <c r="ED2" t="n">
-        <v>3743850</v>
+        <v>0.049999997</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.049999997</v>
-      </c>
-      <c r="EF2" t="n">
         <v>0.26315787</v>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>0.19 - 0.57</t>
         </is>
       </c>
+      <c r="EG2" t="n">
+        <v>-0.32999998</v>
+      </c>
       <c r="EH2" t="n">
-        <v>-0.32999998</v>
+        <v>-0.57894737</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.57894737</v>
+        <v>-22.580647</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-11.111111</v>
+        <v>1732891862</v>
       </c>
       <c r="EK2" t="n">
         <v>1732891862</v>
       </c>
-      <c r="EL2" t="n">
-        <v>1732891862</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+      <c r="EL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.13</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="EO2" t="inlineStr"/>
     </row>
